--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/BONUS-02-ice-cream-shop-seasonal-calendar.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/BONUS-02-ice-cream-shop-seasonal-calendar.xlsx
@@ -633,7 +633,7 @@
     <row r="16">
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>▸ Change any that don't apply where you are and add your town's events (county fairs, summer festivals, high school games): they are what moves a neighborhood scoop shop. UK: Mothering Sunday (March), bank holidays and Boxing Day.</t>
+          <t>▸ Change any that don't apply where you are and add your town's events (county fairs, summer festivals, high school games): they are what moves a neighborhood scoop shop. UK: Mothering Sunday (3 weeks before Easter: March or early April), bank holidays and Boxing Day.</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Easter (date varies): spring flavors and ice cream cakes to order. Expand the menu with fruit flavors. Hire and train the summer team (many are minors: FLSA hours, see the "Peak Season" sheet). Prep the patio and its permit.</t>
+          <t>Easter (date varies): spring flavors and ice cream cakes to order. Expand the menu with fruit flavors. Hire and train the summer team (many are minors: FLSA hours and job limits, see the "Peak Season" sheet). Prep the patio and its permit.</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
